--- a/data/trans_orig/IP25A02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Provincia-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>34284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>51315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>47155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69840</t>
+          <t>69774</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94561</t>
+          <t>94230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>28430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>48700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>40600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33904</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24785</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67347</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>51350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74168</t>
+          <t>74428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75877</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132744</t>
+          <t>132732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83079</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135465</t>
+          <t>134172</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>42836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>61188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>23172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>35619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>47946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>955</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32164</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48104</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29342</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48134</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>45236</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>69990</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>60294</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>87647</t>
+          <t>88845</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47778</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>77057</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>93886</t>
+          <t>94516</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>128945</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>58283</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>67292</t>
+          <t>68667</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>95978</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>71820</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>68666</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>90586</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>127015</t>
+          <t>126629</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>156325</t>
+          <t>155871</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42523</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>72369</t>
+          <t>72573</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,47 +5297,47 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>52450</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>39525</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>52450</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>39431</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>67295</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81984</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>104370</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>145388</t>
+          <t>144303</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>146619</t>
+          <t>145773</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>189452</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>263033</t>
+          <t>259037</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>320881</t>
+          <t>319796</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>222880</t>
+          <t>222479</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>281840</t>
+          <t>283602</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>281039</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>335667</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>518944</t>
+          <t>526724</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>604328</t>
+          <t>604336</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>199722</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>281910</t>
+          <t>286551</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>205142</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>262559</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>418968</t>
+          <t>419302</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>517365</t>
+          <t>527651</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7517</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8331</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9140</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14064</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9423</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11706</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18924</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33226</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26532</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39727</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51,8%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,36%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>61,93%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>42631</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>34284</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51315</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47155</t>
+          <t>36300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>81954</t>
+          <t>63717</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69774</t>
+          <t>54627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94230</t>
+          <t>72014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14170</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19914</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11928</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25523</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>29967</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48700</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9362</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4760</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16265</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4098</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>16974</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>27853</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28142</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19591</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37297</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20713</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9747</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32685</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>18257</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55854</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44381</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67168</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50847</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23927</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68338</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>51020</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74428</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>112572</t>
+          <t>106874</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>94006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132732</t>
+          <t>120980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22478</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15164</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31370</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43851</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19114</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>89847</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134172</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4184</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9086</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9719</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>14102</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21469</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16617</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>24945</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19230</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30879</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>46060</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58213</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26932</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20403</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>21151</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15974</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27251</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42836</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12379</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6253</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21322</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>30,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11032</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6482</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17352</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29944</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>17088</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9291</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26801</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>24,19%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>18396</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>12635</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>25442</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>27,92%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>35956</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>29801</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19999</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45474</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>28278</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>21837</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>35619</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49520</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>58586</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47946</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>73673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,107 +2996,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10705</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27,05%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10534</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>16417</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>20721</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>12587</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>8809</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>16640</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>25,52%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>48,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>29588</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17673</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>13369</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>22399</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>56,59%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>20898</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>16596</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>60,55%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>39046</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>6040</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -3678,72 +3678,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9308</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>14747</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>16496</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>11846</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>21621</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>35,73%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>46,83%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>26275</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>22839</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>16725</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>28424</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>14854</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>10740</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>20382</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>44,15%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32192</t>
+          <t>30484</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>45751</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>13323</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>9452</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>18030</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>12152</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>7942</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>16881</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>28306</t>
+          <t>24372</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>14790</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>9439</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>22653</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>18310</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>11953</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>28302</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46176</t>
+          <t>42338</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>32439</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>23683</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>43073</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>23274</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>16739</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>30984</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>56934</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69990</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>41426</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>31777</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>50764</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>30399</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>22981</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>39819</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>74141</t>
+          <t>72828</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>88845</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>51593</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>42241</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>64063</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>48804</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>39352</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>58673</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>48,58%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>61080</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>48267</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>77057</t>
+          <t>57105</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>109884</t>
+          <t>99229</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>94516</t>
+          <t>85097</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>128945</t>
+          <t>115088</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>120787</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>120787</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>120787</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>275441</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>275441</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>275441</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4703,72 +4703,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>6769</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>6924</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4816,72 +4816,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>48461</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>38135</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>60782</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>34085</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>25517</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>43366</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>48332</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>68667</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>95978</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -4929,72 +4929,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>82976</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>71502</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>94567</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>52,15%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>59,43%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>62051</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>51894</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>71820</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>39,61%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>66415</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>55671</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>91244</t>
+          <t>77329</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>149392</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>126629</t>
+          <t>133835</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>155871</t>
+          <t>166391</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -5042,72 +5042,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>24898</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>18035</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>32860</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>33738</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>26079</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>43611</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>59903</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>72573</t>
+          <t>73596</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -5155,57 +5155,57 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>47629</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>36319</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>61615</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>45624</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>34761</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>61475</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,17 +5347,17 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>76024</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>109243</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>158108</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>137594</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>179232</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>125203</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>103093</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>144303</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>166507</t>
+          <t>124058</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>145773</t>
+          <t>107799</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>188250</t>
+          <t>142008</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>291710</t>
+          <t>282166</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>259037</t>
+          <t>257296</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>319796</t>
+          <t>310418</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -5498,72 +5498,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>291296</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>266619</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>314806</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>362</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>256711</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>222479</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>283602</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>33,99%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>309313</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>227881</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>337426</t>
+          <t>271774</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>566024</t>
+          <t>542231</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>526724</t>
+          <t>513264</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>604336</t>
+          <t>574859</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -5611,72 +5611,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>200868</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>180845</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>228946</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>227042</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>199722</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>286551</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>230524</t>
+          <t>199680</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>179973</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>221831</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>419302</t>
+          <t>371779</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>527651</t>
+          <t>433215</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
